--- a/request_forms/018_string_format_submission_form--request_forms.xlsx
+++ b/request_forms/018_string_format_submission_form--request_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -510,18 +510,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>submission_form</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>submission_form</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Title of the submission</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide the title of the submission</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -538,10 +542,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>examples</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Examples of string formats used</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please provide examples of string formats used in the submission</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -556,15 +564,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>documentation</t>
+          <t>documentation_requirements</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>documentation</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Documentation requirements</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please provide documentation requirements for the submission</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,10 +596,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>supporting_developers</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Supporting developers</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please list the developers supporting the submission</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,10 +623,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>organizing_requirements</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Organizing requirements</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please provide organizing requirements for the submission</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,10 +650,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>technical_requirements</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Technical requirements</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please list technical requirements for the submission</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,10 +677,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>supporting_teams</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Supporting teams</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please list the teams supporting the submission</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,10 +704,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>detailed_specifications</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Detailed specifications</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please provide detailed specifications for the submission</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -694,18 +726,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>data_teams</t>
+          <t>string_format</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>data_teams</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>String format</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please provide the custom string format for the submission</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -717,15 +753,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>qa_teams</t>
+          <t>additional_info</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>qa_teams</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Additional information</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please provide any additional information about the submission</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -740,15 +780,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>custom_string_format</t>
+          <t>supporting_teams_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>custom_string_format</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Supporting Teams 2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please list the teams supporting the submission</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -763,15 +807,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>supporting_developers_0</t>
+          <t>technical_requirements_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>supporting_developers</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Technical requirements 2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please list technical requirements for the submission</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -786,292 +834,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>supporting_teams_0</t>
+          <t>organizing_requirements_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>supporting_teams</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Organizing requirements 2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please list the requirements for organizing the submission</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>detailed_specifications_0</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>detailed_specifications</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>documentation_0</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>documentation</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>qa_teams_0</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>qa_teams</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>technical_requirements_0</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>technical_requirements</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>supporting_developers_1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>supporting_developers</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>supporting_teams_1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>supporting_teams</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>detailed_specifications_1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>detailed_specifications</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>documentation_0</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>documentation</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>qa_teams_1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>qa_teams</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>technical_requirements_0</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>technical_requirements</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>data_teams_0</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>data_teams</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>string_format</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>string_format</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
